--- a/src/tomography_ml_validation/test_data/configs/m8/m8_demo.xlsx
+++ b/src/tomography_ml_validation/test_data/configs/m8/m8_demo.xlsx
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -569,11 +569,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>train</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -637,11 +637,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>train</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -841,11 +841,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -977,11 +977,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>train</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1045,11 +1045,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>train</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.850241465846509</v>
+        <v>7.933552804247341</v>
       </c>
       <c r="D2" t="n">
-        <v>6.245632892902602</v>
+        <v>2.21810383422633</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.624988651116153</v>
+        <v>0.9196096953353248</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -1519,13 +1519,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-2.441970066145657</v>
+        <v>5.600812891778038</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.162201611192253</v>
+        <v>-4.330757323225611</v>
       </c>
       <c r="E3" t="n">
-        <v>19.41459421444757</v>
+        <v>6.063851535321245</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -1563,13 +1563,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.720864599394595</v>
+        <v>-7.025056886707119</v>
       </c>
       <c r="D4" t="n">
-        <v>6.988637818759656</v>
+        <v>-4.030251530387934</v>
       </c>
       <c r="E4" t="n">
-        <v>6.681254539776516</v>
+        <v>6.117110057605364</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-8.396472094965622</v>
+        <v>7.906660367444804</v>
       </c>
       <c r="D5" t="n">
-        <v>1.558901584662507</v>
+        <v>1.164968123065188</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.31880527381743</v>
+        <v>7.789656480269313</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.310378117328352</v>
+        <v>5.851819461564727</v>
       </c>
       <c r="D6" t="n">
-        <v>-5.728873036470876</v>
+        <v>-7.115807410724962</v>
       </c>
       <c r="E6" t="n">
-        <v>7.295246426509847</v>
+        <v>4.005470311515367</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-4.574736578160636</v>
+        <v>-6.454381812875152</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1626674150571024</v>
+        <v>1.487233878653155</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.008587502803895752</v>
+        <v>-3.666478588834543</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-10.99330289073408</v>
+        <v>-2.426374721722151</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03816720108044969</v>
+        <v>1.575742412071584</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9776747581115064</v>
+        <v>-1.86058490701526</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -1783,13 +1783,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.413289220034144</v>
+        <v>-5.349501806171361</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8187441953142045</v>
+        <v>0.5458901236100342</v>
       </c>
       <c r="E9" t="n">
-        <v>16.93598216655483</v>
+        <v>3.007623204664336</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.225852260144737</v>
+        <v>-3.310529750398716</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.345253111586654</v>
+        <v>-1.27613912961047</v>
       </c>
       <c r="E10" t="n">
-        <v>16.92496002390521</v>
+        <v>-2.541750477992224</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.014329928374099</v>
+        <v>-6.753859229630599</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.824476953521907</v>
+        <v>-7.994371165148222</v>
       </c>
       <c r="E11" t="n">
-        <v>2.595683633694051</v>
+        <v>3.442692052364817</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
